--- a/docs/downloads/20261001_Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20261001_Johor_Teduh_Weekly_Update.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AY21"/>
+  <dimension ref="A2:BB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -547,7 +547,10 @@
     <col width="9" customWidth="1" min="48" max="48"/>
     <col width="9" customWidth="1" min="49" max="49"/>
     <col width="9" customWidth="1" min="50" max="50"/>
-    <col width="46" customWidth="1" min="51" max="51"/>
+    <col width="9" customWidth="1" min="51" max="51"/>
+    <col width="9" customWidth="1" min="52" max="52"/>
+    <col width="9" customWidth="1" min="53" max="53"/>
+    <col width="46" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -605,8 +608,11 @@
       <c r="AS3" s="3" t="n">
         <v>46283</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AV3" s="3" t="n">
         <v>46290</v>
+      </c>
+      <c r="AY3" s="4" t="n">
+        <v>46297</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -847,22 +853,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AV4" s="6" t="inlineStr">
+      <c r="AV4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AW4" s="6" t="inlineStr">
+      <c r="AW4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AX4" s="6" t="inlineStr">
+      <c r="AX4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AY4" s="5" t="inlineStr">
+      <c r="AY4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AZ4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BA4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="BB4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -924,6 +945,9 @@
       <c r="AW5" s="8" t="n"/>
       <c r="AX5" s="8" t="n"/>
       <c r="AY5" s="8" t="n"/>
+      <c r="AZ5" s="8" t="n"/>
+      <c r="BA5" s="8" t="n"/>
+      <c r="BB5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1096,20 +1120,31 @@
         <f>AT6/$D$6</f>
         <v/>
       </c>
-      <c r="AV6" s="14">
+      <c r="AV6" s="12">
         <f>AW6-AT6</f>
         <v/>
       </c>
-      <c r="AW6" s="14" t="n">
+      <c r="AW6" s="12" t="n">
         <v>321</v>
       </c>
-      <c r="AX6" s="15">
+      <c r="AX6" s="13">
         <f>AW6/$D$6</f>
         <v/>
       </c>
-      <c r="AY6" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 195 units, Block B: 126 units</t>
+      <c r="AY6" s="14">
+        <f>AZ6-AW6</f>
+        <v/>
+      </c>
+      <c r="AZ6" s="14" t="n">
+        <v>328</v>
+      </c>
+      <c r="BA6" s="15">
+        <f>AZ6/$D$6</f>
+        <v/>
+      </c>
+      <c r="BB6" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 196 units, Block B: 132 units</t>
         </is>
       </c>
     </row>
@@ -1284,20 +1319,31 @@
         <f>AT7/$D$7</f>
         <v/>
       </c>
-      <c r="AV7" s="14">
+      <c r="AV7" s="12">
         <f>AW7-AT7</f>
         <v/>
       </c>
-      <c r="AW7" s="14" t="n">
+      <c r="AW7" s="12" t="n">
         <v>1007</v>
       </c>
-      <c r="AX7" s="15">
+      <c r="AX7" s="13">
         <f>AW7/$D$7</f>
         <v/>
       </c>
-      <c r="AY7" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 415 units, Block B: 391 units, Block C: 91 units, Block D: 110 units</t>
+      <c r="AY7" s="14">
+        <f>AZ7-AW7</f>
+        <v/>
+      </c>
+      <c r="AZ7" s="14" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BA7" s="15">
+        <f>AZ7/$D$7</f>
+        <v/>
+      </c>
+      <c r="BB7" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 417 units, Block B: 394 units, Block C: 92 units, Block D: 114 units</t>
         </is>
       </c>
     </row>
@@ -1472,18 +1518,29 @@
         <f>AT8/$D$8</f>
         <v/>
       </c>
-      <c r="AV8" s="14">
+      <c r="AV8" s="12">
         <f>AW8-AT8</f>
         <v/>
       </c>
-      <c r="AW8" s="14" t="n">
+      <c r="AW8" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="AX8" s="15">
+      <c r="AX8" s="13">
         <f>AW8/$D$8</f>
         <v/>
       </c>
-      <c r="AY8" s="10" t="inlineStr">
+      <c r="AY8" s="14">
+        <f>AZ8-AW8</f>
+        <v/>
+      </c>
+      <c r="AZ8" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BA8" s="15">
+        <f>AZ8/$D$8</f>
+        <v/>
+      </c>
+      <c r="BB8" s="10" t="inlineStr">
         <is>
           <t>Open sale for Block A (416 units) only; tracked against the full development</t>
         </is>
@@ -1660,20 +1717,31 @@
         <f>AT9/$D$9</f>
         <v/>
       </c>
-      <c r="AV9" s="14">
+      <c r="AV9" s="12">
         <f>AW9-AT9</f>
         <v/>
       </c>
-      <c r="AW9" s="14" t="n">
+      <c r="AW9" s="12" t="n">
         <v>1086</v>
       </c>
-      <c r="AX9" s="15">
+      <c r="AX9" s="13">
         <f>AW9/$D$9</f>
         <v/>
       </c>
-      <c r="AY9" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Phase 1: 671 units, Phase 2: 415 units</t>
+      <c r="AY9" s="14">
+        <f>AZ9-AW9</f>
+        <v/>
+      </c>
+      <c r="AZ9" s="14" t="n">
+        <v>1091</v>
+      </c>
+      <c r="BA9" s="15">
+        <f>AZ9/$D$9</f>
+        <v/>
+      </c>
+      <c r="BB9" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Phase 1: 671 units, Phase 2: 420 units</t>
         </is>
       </c>
     </row>
@@ -1733,6 +1801,9 @@
       <c r="AW10" s="8" t="n"/>
       <c r="AX10" s="8" t="n"/>
       <c r="AY10" s="8" t="n"/>
+      <c r="AZ10" s="8" t="n"/>
+      <c r="BA10" s="8" t="n"/>
+      <c r="BB10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1905,18 +1976,29 @@
         <f>AT11/$D$11</f>
         <v/>
       </c>
-      <c r="AV11" s="14">
+      <c r="AV11" s="12">
         <f>AW11-AT11</f>
         <v/>
       </c>
-      <c r="AW11" s="14" t="n">
+      <c r="AW11" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="AX11" s="15">
+      <c r="AX11" s="13">
         <f>AW11/$D$11</f>
         <v/>
       </c>
-      <c r="AY11" s="10" t="inlineStr">
+      <c r="AY11" s="14">
+        <f>AZ11-AW11</f>
+        <v/>
+      </c>
+      <c r="AZ11" s="14" t="n">
+        <v>844</v>
+      </c>
+      <c r="BA11" s="15">
+        <f>AZ11/$D$11</f>
+        <v/>
+      </c>
+      <c r="BB11" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2093,20 +2175,31 @@
         <f>AT12/$D$12</f>
         <v/>
       </c>
-      <c r="AV12" s="14">
+      <c r="AV12" s="12">
         <f>AW12-AT12</f>
         <v/>
       </c>
-      <c r="AW12" s="14" t="n">
+      <c r="AW12" s="12" t="n">
         <v>1559</v>
       </c>
-      <c r="AX12" s="15">
+      <c r="AX12" s="13">
         <f>AW12/$D$12</f>
         <v/>
       </c>
-      <c r="AY12" s="10" t="inlineStr">
-        <is>
-          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 527 units, Block B: 538 units, Block D: 494 units</t>
+      <c r="AY12" s="14">
+        <f>AZ12-AW12</f>
+        <v/>
+      </c>
+      <c r="AZ12" s="14" t="n">
+        <v>1569</v>
+      </c>
+      <c r="BA12" s="15">
+        <f>AZ12/$D$12</f>
+        <v/>
+      </c>
+      <c r="BB12" s="10" t="inlineStr">
+        <is>
+          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 533 units, Block B: 541 units, Block D: 495 units</t>
         </is>
       </c>
     </row>
@@ -2281,20 +2374,31 @@
         <f>AT13/$D$13</f>
         <v/>
       </c>
-      <c r="AV13" s="14">
+      <c r="AV13" s="12">
         <f>AW13-AT13</f>
         <v/>
       </c>
-      <c r="AW13" s="14" t="n">
+      <c r="AW13" s="12" t="n">
         <v>1045</v>
       </c>
-      <c r="AX13" s="15">
+      <c r="AX13" s="13">
         <f>AW13/$D$13</f>
         <v/>
       </c>
-      <c r="AY13" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 408 units, Block B: 380 units, Block C: 257 units</t>
+      <c r="AY13" s="14">
+        <f>AZ13-AW13</f>
+        <v/>
+      </c>
+      <c r="AZ13" s="14" t="n">
+        <v>1064</v>
+      </c>
+      <c r="BA13" s="15">
+        <f>AZ13/$D$13</f>
+        <v/>
+      </c>
+      <c r="BB13" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 412 units, Block B: 384 units, Block C: 268 units</t>
         </is>
       </c>
     </row>
@@ -2469,20 +2573,31 @@
         <f>AT14/$D$14</f>
         <v/>
       </c>
-      <c r="AV14" s="14">
+      <c r="AV14" s="12">
         <f>AW14-AT14</f>
         <v/>
       </c>
-      <c r="AW14" s="14" t="n">
+      <c r="AW14" s="12" t="n">
         <v>797</v>
       </c>
-      <c r="AX14" s="15">
+      <c r="AX14" s="13">
         <f>AW14/$D$14</f>
         <v/>
       </c>
-      <c r="AY14" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 516 units, Block B: 281 units</t>
+      <c r="AY14" s="14">
+        <f>AZ14-AW14</f>
+        <v/>
+      </c>
+      <c r="AZ14" s="14" t="n">
+        <v>813</v>
+      </c>
+      <c r="BA14" s="15">
+        <f>AZ14/$D$14</f>
+        <v/>
+      </c>
+      <c r="BB14" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 526 units, Block B: 287 units</t>
         </is>
       </c>
     </row>
@@ -2657,20 +2772,31 @@
         <f>AT15/$D$15</f>
         <v/>
       </c>
-      <c r="AV15" s="14">
+      <c r="AV15" s="12">
         <f>AW15-AT15</f>
         <v/>
       </c>
-      <c r="AW15" s="14" t="n">
+      <c r="AW15" s="12" t="n">
         <v>1409</v>
       </c>
-      <c r="AX15" s="15">
+      <c r="AX15" s="13">
         <f>AW15/$D$15</f>
         <v/>
       </c>
-      <c r="AY15" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 731 units, Block B: 678 units</t>
+      <c r="AY15" s="14">
+        <f>AZ15-AW15</f>
+        <v/>
+      </c>
+      <c r="AZ15" s="14" t="n">
+        <v>1415</v>
+      </c>
+      <c r="BA15" s="15">
+        <f>AZ15/$D$15</f>
+        <v/>
+      </c>
+      <c r="BB15" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 732 units, Block B: 683 units</t>
         </is>
       </c>
     </row>
@@ -2845,18 +2971,29 @@
         <f>AT16/$D$16</f>
         <v/>
       </c>
-      <c r="AV16" s="14">
+      <c r="AV16" s="12">
         <f>AW16-AT16</f>
         <v/>
       </c>
-      <c r="AW16" s="14" t="n">
+      <c r="AW16" s="12" t="n">
         <v>917</v>
       </c>
-      <c r="AX16" s="15">
+      <c r="AX16" s="13">
         <f>AW16/$D$16</f>
         <v/>
       </c>
-      <c r="AY16" s="10" t="inlineStr">
+      <c r="AY16" s="14">
+        <f>AZ16-AW16</f>
+        <v/>
+      </c>
+      <c r="AZ16" s="14" t="n">
+        <v>922</v>
+      </c>
+      <c r="BA16" s="15">
+        <f>AZ16/$D$16</f>
+        <v/>
+      </c>
+      <c r="BB16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2983,10 +3120,13 @@
       <c r="AS17" s="12" t="n"/>
       <c r="AT17" s="12" t="n"/>
       <c r="AU17" s="13" t="n"/>
-      <c r="AV17" s="14" t="n"/>
-      <c r="AW17" s="14" t="n"/>
-      <c r="AX17" s="15" t="n"/>
-      <c r="AY17" s="10" t="inlineStr">
+      <c r="AV17" s="12" t="n"/>
+      <c r="AW17" s="12" t="n"/>
+      <c r="AX17" s="13" t="n"/>
+      <c r="AY17" s="14" t="n"/>
+      <c r="AZ17" s="14" t="n"/>
+      <c r="BA17" s="15" t="n"/>
+      <c r="BB17" s="10" t="inlineStr">
         <is>
           <t>*No info on Teduh, Not obtained AP.</t>
         </is>
@@ -3163,20 +3303,31 @@
         <f>AT18/$D$18</f>
         <v/>
       </c>
-      <c r="AV18" s="14">
+      <c r="AV18" s="12">
         <f>AW18-AT18</f>
         <v/>
       </c>
-      <c r="AW18" s="14" t="n">
+      <c r="AW18" s="12" t="n">
         <v>742</v>
       </c>
-      <c r="AX18" s="15">
+      <c r="AX18" s="13">
         <f>AW18/$D$18</f>
         <v/>
       </c>
-      <c r="AY18" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 452 units, Block B: 290 units</t>
+      <c r="AY18" s="14">
+        <f>AZ18-AW18</f>
+        <v/>
+      </c>
+      <c r="AZ18" s="14" t="n">
+        <v>745</v>
+      </c>
+      <c r="BA18" s="15">
+        <f>AZ18/$D$18</f>
+        <v/>
+      </c>
+      <c r="BB18" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 455 units, Block B: 290 units</t>
         </is>
       </c>
     </row>
@@ -3351,20 +3502,31 @@
         <f>AT19/$D$19</f>
         <v/>
       </c>
-      <c r="AV19" s="14">
+      <c r="AV19" s="12">
         <f>AW19-AT19</f>
         <v/>
       </c>
-      <c r="AW19" s="14" t="n">
+      <c r="AW19" s="12" t="n">
         <v>402</v>
       </c>
-      <c r="AX19" s="15">
+      <c r="AX19" s="13">
         <f>AW19/$D$19</f>
         <v/>
       </c>
-      <c r="AY19" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 301 units, Block B: 101 units</t>
+      <c r="AY19" s="14">
+        <f>AZ19-AW19</f>
+        <v/>
+      </c>
+      <c r="AZ19" s="14" t="n">
+        <v>407</v>
+      </c>
+      <c r="BA19" s="15">
+        <f>AZ19/$D$19</f>
+        <v/>
+      </c>
+      <c r="BB19" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 301 units, Block B: 106 units</t>
         </is>
       </c>
     </row>
@@ -3539,20 +3701,31 @@
         <f>AT20/$D$20</f>
         <v/>
       </c>
-      <c r="AV20" s="14">
+      <c r="AV20" s="12">
         <f>AW20-AT20</f>
         <v/>
       </c>
-      <c r="AW20" s="14" t="n">
+      <c r="AW20" s="12" t="n">
         <v>331</v>
       </c>
-      <c r="AX20" s="15">
+      <c r="AX20" s="13">
         <f>AW20/$D$20</f>
         <v/>
       </c>
-      <c r="AY20" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 227 units, Block B: 104 units</t>
+      <c r="AY20" s="14">
+        <f>AZ20-AW20</f>
+        <v/>
+      </c>
+      <c r="AZ20" s="14" t="n">
+        <v>333</v>
+      </c>
+      <c r="BA20" s="15">
+        <f>AZ20/$D$20</f>
+        <v/>
+      </c>
+      <c r="BB20" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 227 units, Block B: 106 units</t>
         </is>
       </c>
     </row>
@@ -3631,21 +3804,33 @@
         <f>AT21/$D$21</f>
         <v/>
       </c>
-      <c r="AV21" s="14">
+      <c r="AV21" s="12">
         <f>AW21-AT21</f>
         <v/>
       </c>
-      <c r="AW21" s="14" t="n">
+      <c r="AW21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="AX21" s="15">
+      <c r="AX21" s="13">
         <f>AW21/$D$21</f>
         <v/>
       </c>
-      <c r="AY21" s="10" t="inlineStr"/>
+      <c r="AY21" s="14">
+        <f>AZ21-AW21</f>
+        <v/>
+      </c>
+      <c r="AZ21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" s="15">
+        <f>AZ21/$D$21</f>
+        <v/>
+      </c>
+      <c r="BB21" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="AY3:BA3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="AD3:AF3"/>
